--- a/Results/Two_Datasets_Assessment/Cancer/Tables/generator_summary.xlsx
+++ b/Results/Two_Datasets_Assessment/Cancer/Tables/generator_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
           <t>OverallScore_Formatted</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_Formatted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -493,13 +498,13 @@
         <v>0.968362898094103</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2648177399141864</v>
+        <v>0.4849657455036203</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7458789484729241</v>
+        <v>0.7279601106252133</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6905541657537744</v>
+        <v>0.7512229160762912</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -511,197 +516,222 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.2648</t>
+          <t>0.4850</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>\textbf{0.7459}</t>
+          <t>\underline{0.7280}</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>\textbf{0.6906}</t>
+          <t>\textbf{0.7512}</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>\textbf{1.0000}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8534899925686222</v>
+        <v>0.9355254935904923</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5133862651733053</v>
+        <v>0.4785157516103453</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5363147907251201</v>
+        <v>0.7262959665789475</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6563063137969766</v>
+        <v>0.7356537128929848</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.8535</t>
+          <t>\underline{0.9355}</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>\underline{0.5134}</t>
+          <t>0.4785</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.5363</t>
+          <t>0.7263</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>\underline{0.6563}</t>
+          <t>\underline{0.7357}</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>\underline{2.0000}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9230599709384475</v>
+        <v>0.8200940787089187</v>
       </c>
       <c r="D4" t="n">
-        <v>0.413774075177361</v>
+        <v>0.519908292713704</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4877173849809624</v>
+        <v>0.8121587739421542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.639671426422876</v>
+        <v>0.7276577514803249</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.9231</t>
+          <t>0.8201</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.4138</t>
+          <t>0.5199</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.4877</t>
+          <t>\textbf{0.8122}</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.6397</t>
+          <t>0.7277</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3.0000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8200940787089187</v>
+        <v>0.9230599709384475</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3928241452145236</v>
+        <v>0.5372078162303315</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6147824256659962</v>
+        <v>0.5817496483258702</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6303196027477234</v>
+        <v>0.7049112277422396</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8201</t>
+          <t>0.9231</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.3928</t>
+          <t>\textbf{0.5372}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>\underline{0.6148}</t>
+          <t>0.5817</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6303</t>
+          <t>0.7049</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4.0000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9355254935904923</v>
+        <v>0.8534899925686222</v>
       </c>
       <c r="D6" t="n">
-        <v>0.255724578002569</v>
+        <v>0.5275669612932169</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5695028378343651</v>
+        <v>0.6670557325674165</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6217784221872772</v>
+        <v>0.699782805185639</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>\underline{0.9355}</t>
+          <t>0.8535</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.2557</t>
+          <t>\underline{0.5276}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.5695</t>
+          <t>0.6671</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.6218</t>
+          <t>0.6998</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5.0000</t>
         </is>
       </c>
     </row>
@@ -718,13 +748,13 @@
         <v>0.7038964675556111</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4750360720991947</v>
+        <v>0.4872794696822143</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3123008246014149</v>
+        <v>0.2013340430684206</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5177596560324272</v>
+        <v>0.4881426408474349</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -736,17 +766,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.4750</t>
+          <t>0.4873</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.3123</t>
+          <t>0.2013</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.5178</t>
+          <t>0.4881</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.0000</t>
         </is>
       </c>
     </row>
@@ -763,13 +798,13 @@
         <v>0.3220413157082996</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5143939653183046</v>
+        <v>0.4629545687864741</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4597927818721145</v>
+        <v>0.7201306164880913</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4210725504404456</v>
+        <v>0.4837420818656895</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
@@ -781,17 +816,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>\textbf{0.5144}</t>
+          <t>0.4630</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.4598</t>
+          <t>0.7201</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.4211</t>
+          <t>0.4837</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7.0000</t>
         </is>
       </c>
     </row>
@@ -808,13 +848,13 @@
         <v>0.3729653880480129</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3682877872336551</v>
+        <v>0.493020634446126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3801171918778428</v>
+        <v>0.1717370163302168</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3737076489526545</v>
+        <v>0.348613450452108</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
@@ -826,17 +866,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.3683</t>
+          <t>0.4930</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.3801</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.3737</t>
+          <t>0.3486</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8.0000</t>
         </is>
       </c>
     </row>
